--- a/SantanderCS/results/ResultListByTestModel_lsj.xlsx
+++ b/SantanderCS/results/ResultListByTestModel_lsj.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD329C8-3896-4D7C-A3BB-85FF7A7A7589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3029E3F8-A265-481D-AD66-08172E1712A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
   </bookViews>
@@ -33,8 +33,172 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>TJ</author>
+  </authors>
+  <commentList>
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{B062AA88-C748-44AB-933C-4E24020FE7D7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">rf_clf = RandomForestClassifier(
+    random_state      = 23,
+    n_estimators      = 390,
+    max_depth         = 25,
+    class_weight      = {0:1, 1:2},
+    min_samples_leaf  = 1,
+    min_samples_split = 7,
+    n_jobs            = -1
+)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+xgb_clf = XGBClassifier(
+    random_state      = 23,    
+    n_estimators      = 320,
+    colsample_bytree  = 0.88,
+    gamma             = 0.058, 
+    learning_rate     = 0.13,
+    max_depth         = 6,
+    scale_pos_weight  = 10,
+    min_child_weight  = 2, 
+    subsample         = 0.85,    
+    eval_metric       ='auc',
+    use_label_encoder = False,
+    n_jobs            = -1,
+)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">np.float64(0.973776538266153)}
+lgbm_clf = LGBMClassifier(
+    random_state = 0,
+    n_estimators = 400,
+    num_leaves = 36,
+    learning_rate = 0.03,
+    subsample = 0.9,
+    colsample_bytree = 0.75,
+    reg_alpha = 0.6,
+    reg_lambda = 0.2,
+    class_weight = {0:1, 1:10},
+    n_jobs = -1
+)
+# 2. Meta model </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">정의
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>meta_model = LogisticRegression(
+    random_state = 23,
+    max_iter     = 1000,
+    class_weight="balanced"
+)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0" xr:uid="{2FAA2EE8-73F8-4EF2-A2FB-AD583E875E79}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>rf_clf = RandomForestClassifier(
+    random_state      = 23,
+    n_estimators      = 390,
+    max_depth         = 25,
+    class_weight      = {0:1, 1:2},
+    min_samples_leaf  = 1,
+    min_samples_split = 7,
+    n_jobs            = -1
+)
+xgb_clf = XGBClassifier(
+    random_state      = 23,    
+    n_estimators      = 320,
+    colsample_bytree  = 0.88,
+    gamma             = 0.058, 
+    learning_rate     = 0.13,
+    max_depth         = 6,
+    scale_pos_weight  = 10,
+    min_child_weight  = 2, 
+    subsample         = 0.85,    
+    eval_metric       ='auc',
+    use_label_encoder = False,
+    n_jobs            = -1,
+)
+lgbm_clf = LGBMClassifier(
+    random_state     = 23,
+    n_estimators     = 300,
+    colsample_bytree = 0.73,
+    # max_depth      = -1,
+    learning_rate    = 0.03,
+    num_leaves       = 42,
+    reg_alpha        = 0.61,
+    reg_lambda       = 0.13,
+    subsample        = 0.97,
+    class_weight     = {0:1, 1:10},
+    n_jobs           = -1,
+)
+meta_model = LogisticRegression(
+    random_state = 23,
+    max_iter     = 1000,
+    C            = 0.029,
+    penalty      = 'l2',
+    solver       = 'lbfgs',
+    class_weight ="balanced"
+    # **lr_best_param
+)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
   <si>
     <t>NO</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -82,6 +246,275 @@
   <si>
     <t xml:space="preserve">Var3, 
 Zero_Count_Rate &gt; 99% 컬럼 삭제 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(76020, 149)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(
+  random_state      = 0,
+  n_estimators      = 100,
+  num_leaves        = 15,        # 가지 수
+  min_child_samples = 2
+)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lgbm_99per_basic.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Scaled /
+ZCR &gt; 99% +
+Corr() &gt; 95% 컬럼 삭제/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(76020, 96)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(
+        random_state      = 0,
+        n_estimators      = 300,
+        num_leaves        = 32,        # 가지 수
+        min_child_samples = 24,
+        class_weight = {0:1, 1:2},
+        verbose           = -1
+    )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_99per_Corr_weight12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(
+        random_state      = 0,
+        n_estimators      = 500,
+        num_leaves        = 32,   
+        min_child_samples = 18,         
+        class_weight      = {0:1, 1:5}, 
+        learning_rate     = 0.05,
+        subsample         = 0.8,
+        colsample_bytree  = 0.8, 
+        verbose           = -1 
+    )
+    </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_99per_Corr_weight15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(18048, 94)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Scaled /
+ZCR &gt; 99% +
+Corr() &gt; 95% 컬럼 삭제/
+UnderSampling_Ratio=5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(
+    random_state = 0,
+    n_estimators = 400,
+    num_leaves = 36,
+    learning_rate = 0.03,
+    subsample = 0.9,
+    colsample_bytree = 0.75,
+    reg_alpha = 0.6,
+    reg_lambda = 0.2,
+    class_weight = {0:1, 1:10}
+)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Scaled /
+ZCR &gt; 99% +
+Corr() &gt; 95% 컬럼 삭제/
+UnderSampling_Ratio=10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 / Scaled /
+ZCR &gt; 99% +
+Corr() &gt; 95% 컬럼 삭제/
+UnderSampling_Ratio=20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(33088, 94)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(63168, 94)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_99per_corrTh95_UnderSampling5_BestOpt.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>models\LightGBM_99per_corrTh95_UnderSampling10_BestOpt.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_99per_corrTh95_UnderSampling20_BestOpt.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 /Scaled + K-Fold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(
+            random_state = 0,
+            n_estimators = 400,
+            num_leaves = 36,
+            learning_rate = 0.03,
+            subsample = 0.9,
+            colsample_bytree = 0.75,
+            reg_alpha = 0.6,
+            reg_lambda = 0.2,
+            class_weight = {0:1, 1:20}
+        )   </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=== Stratified K-Fold 평균 성능 ===
+ROC-AUC 평균: 0.8125
+PR-AUC 평균:  0.1721
+F1 평균:      0.2414
+Recall 평균:  0.5934</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=== Stratified K-Fold 평균 성능 ===
+ROC-AUC 평균: 0.8177
+PR-AUC 평균:  0.1755
+F1 평균:      0.2674
+Recall 평균:  0.4927</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=== Stratified K-Fold 평균 성능 ===
+ROC-AUC 평균: 0.8217
+PR-AUC 평균:  0.1757
+F1 평균:      0.2615
+Recall 평균:  0.3364</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(
+    random_state      = 0,
+    n_estimators      = 500,
+    num_leaves        = 32,         
+    min_child_samples = 18,             
+    class_weight      = {0:1, 1:5}, 
+    learning_rate     = 0.05, 
+    subsample         = 0.8, 
+    colsample_bytree  = 0.8, 
+    verbose           = -1 
+)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Var3 /Scaled + FeatureAdd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_99per_FE_scaled_ne500_nl23_mcs18_classweight15_lr05_ss08.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(76020, 99)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Var3 / Scaled </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lgbm_99per_basic7vs3.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(
+        random_state = 0,
+        n_estimators = 400,
+        num_leaves = 36,
+        learning_rate = 0.03,
+        subsample = 0.9,
+        colsample_bytree = 0.75,
+        reg_alpha = 0.6,
+        reg_lambda = 0.2,
+        class_weight = {0:1, 1:10},
+        n_jobs = -1
+    )</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LightGBM_99per_Corr_weight110.pkl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Var3 / Scaled /
+log1p(71개 피쳐)
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stacking</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Var3 / Scaled /
+log변환X
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stacking_model = StackingClassifier(
+    estimators      = [('rf', rf_clf), ('xgb', xgb_clf), ('lgbm', lgbm_clf)],
+    final_estimator = meta_model,
+    cv              = StratifiedKFold(n_splits=5, shuffle=True, random_state=42),
+    n_jobs          = -1
+) *메모참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stacking_model = StackingClassifier(
+    estimators      = [('rf', rf_clf), ('xgb', xgb_clf), ('lgbm', lgbm_clf)],
+    final_estimator = meta_model,
+    cv              = StratifiedKFold(n_splits=5, shuffle=True, random_state=42),
+    n_jobs          = -1
+)*메모참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StackingModel_RF+LGBM+XGB_20251123.pkl
+RandomForest 기여도(계수): 2.3591
+XGBoost 기여도(계수): -2.1535
+LightGBM 기여도(계수): 6.2372
+Stacking 모델 ROC-AUC: 0.9115
+Stacking 모델 F1-Score: 0.2797
+Stacking 모델 Recall:   0.8557</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StackingModel_log1p_RF+LGBM+XGB+LR_20251125-final.pkl
+RandomForest 기여도(계수): 1.8603
+XGBoost 기여도(계수): -0.6759
+LightGBM 기여도(계수): 4.8092
+Stacking 모델 ROC-AUC: 0.9300
+Stacking 모델 F1-Score: 0.2933
+Stacking 모델 Recall:   0.8853</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -89,7 +522,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,6 +537,35 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="5">
@@ -132,7 +594,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -254,36 +716,10 @@
     <border>
       <left/>
       <right style="hair">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -292,7 +728,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -335,32 +771,65 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -675,8 +1144,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA66AA66-968F-43FC-BD0D-4CB9ADC09730}">
-  <dimension ref="A1:J297"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA66AA66-968F-43FC-BD0D-4CB9ADC09730}">
+  <dimension ref="A1:L297"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.875" style="2" bestFit="1" customWidth="1"/>
@@ -688,334 +1157,511 @@
     <col min="7" max="7" width="9.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="8.75" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="56.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="69.75" style="29" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="25" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11">
+    <row r="2" spans="1:12" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="5">
         <v>0.2</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="13" t="s">
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="22"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="11">
+      <c r="F2" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.84570000000000001</v>
+      </c>
+      <c r="H2" s="16">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="I2" s="16">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="J2" s="26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="5">
         <v>0.2</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="22"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <f t="shared" ref="A4:A17" si="0">A3+1</f>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.83374000000000004</v>
+      </c>
+      <c r="H3" s="5">
+        <v>4.8411000000000003E-2</v>
+      </c>
+      <c r="I3" s="5">
+        <v>2.6578000000000001E-2</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="20"/>
+    </row>
+    <row r="4" spans="1:12" ht="198" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <f t="shared" ref="A4:A14" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="5">
         <v>0.2</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0.83463600000000004</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.28441</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.362126</v>
+      </c>
+      <c r="J4" s="27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="5">
         <v>0.2</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="D5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.51739999999999997</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.64119999999999999</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="5">
         <v>0.2</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.81789999999999996</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.40849999999999997</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.54149999999999998</v>
+      </c>
+      <c r="J6" s="27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="5">
         <v>0.2</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="D7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.81730000000000003</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.30709999999999998</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.42520000000000002</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="5">
         <v>0.2</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="5"/>
+      <c r="D8" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>32</v>
+      </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="I8" s="4"/>
+      <c r="J8" s="28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="5">
         <v>0.2</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
+      <c r="D9" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>32</v>
+      </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+      <c r="I9" s="4"/>
+      <c r="J9" s="28" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="5">
         <v>0.2</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
+      <c r="D10" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>32</v>
+      </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="I10" s="4"/>
+      <c r="J10" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="5">
         <v>0.2</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+      <c r="D11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.83640000000000003</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.29070000000000001</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.37040000000000001</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="18">
-        <v>0.2</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+      <c r="C12" s="24">
+        <v>0.3</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="33">
+        <v>0.83740000000000003</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="J12" s="29" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="198" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="5">
         <v>0.2</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="6"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+      <c r="D13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.84520600000000001</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.287053</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.55980099999999999</v>
+      </c>
+      <c r="J13" s="27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="18">
+      <c r="B14" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="5">
         <v>0.2</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="6"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
+      <c r="D14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0.91149999999999998</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0.2797</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.85570000000000002</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
         <f>A14+1</f>
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="18">
+      <c r="B15" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="5">
         <v>0.2</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="6"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="18">
-        <v>0.2</v>
-      </c>
+      <c r="D15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="31">
+        <v>0.93</v>
+      </c>
+      <c r="H15" s="31">
+        <v>0.29330000000000001</v>
+      </c>
+      <c r="I15" s="32">
+        <v>0.88529999999999998</v>
+      </c>
+      <c r="J15" s="30" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="4"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="5"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="18">
-        <v>0.2</v>
-      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="27"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="4"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="6"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="27"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -1023,10 +1669,11 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
-      <c r="I18" s="6"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="27"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -1034,10 +1681,11 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
-      <c r="I19" s="6"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="27"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -1045,10 +1693,11 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="6"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="27"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -1056,10 +1705,11 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="6"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="27"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -1067,10 +1717,11 @@
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="27"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -1078,10 +1729,11 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
-      <c r="I23" s="6"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="27"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -1089,10 +1741,11 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
-      <c r="I24" s="6"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="3"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="27"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -1100,10 +1753,11 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="6"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="3"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="27"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -1111,10 +1765,11 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
-      <c r="I26" s="6"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="3"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="27"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -1122,10 +1777,11 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
-      <c r="I27" s="6"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="3"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="27"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -1133,10 +1789,11 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
-      <c r="I28" s="6"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="27"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -1144,10 +1801,11 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
-      <c r="I29" s="6"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="3"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="27"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -1155,10 +1813,11 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
-      <c r="I30" s="6"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="3"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="27"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -1166,10 +1825,11 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
-      <c r="I31" s="6"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="3"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="27"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -1177,10 +1837,11 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
-      <c r="I32" s="6"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="3"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="27"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
@@ -1188,10 +1849,11 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
-      <c r="I33" s="6"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="3"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="27"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -1199,10 +1861,11 @@
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
-      <c r="I34" s="6"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="3"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="27"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -1210,10 +1873,11 @@
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
-      <c r="I35" s="6"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="3"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="27"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -1221,10 +1885,11 @@
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
-      <c r="I36" s="6"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="3"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="27"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -1232,10 +1897,11 @@
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
-      <c r="I37" s="6"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="3"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="27"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -1243,10 +1909,11 @@
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
-      <c r="I38" s="6"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="3"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="27"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -1254,10 +1921,11 @@
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
-      <c r="I39" s="6"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="3"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="27"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -1265,10 +1933,11 @@
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
-      <c r="I40" s="6"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="3"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="27"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -1276,10 +1945,11 @@
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
-      <c r="I41" s="6"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="3"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="27"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -1287,10 +1957,11 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
-      <c r="I42" s="6"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" s="3"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="27"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -1298,10 +1969,11 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
-      <c r="I43" s="6"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" s="3"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="27"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -1309,10 +1981,11 @@
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
-      <c r="I44" s="6"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" s="3"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="27"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -1320,10 +1993,11 @@
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
-      <c r="I45" s="6"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" s="3"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="27"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -1331,10 +2005,11 @@
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
-      <c r="I46" s="6"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" s="3"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="27"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -1342,10 +2017,11 @@
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
-      <c r="I47" s="6"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" s="3"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="27"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -1353,10 +2029,11 @@
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
-      <c r="I48" s="6"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="3"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="27"/>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -1364,10 +2041,11 @@
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
-      <c r="I49" s="6"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="3"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="27"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -1375,10 +2053,11 @@
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
-      <c r="I50" s="6"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="3"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="27"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -1386,20 +2065,21 @@
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
-      <c r="I51" s="6"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="3"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="6"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I51" s="4"/>
+      <c r="J51" s="27"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="11"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+      <c r="H52" s="15"/>
+      <c r="I52" s="19"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -1410,7 +2090,7 @@
       <c r="H53" s="5"/>
       <c r="I53" s="6"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -1421,7 +2101,7 @@
       <c r="H54" s="5"/>
       <c r="I54" s="6"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -1432,7 +2112,7 @@
       <c r="H55" s="5"/>
       <c r="I55" s="6"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -1443,7 +2123,7 @@
       <c r="H56" s="5"/>
       <c r="I56" s="6"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -1454,7 +2134,7 @@
       <c r="H57" s="5"/>
       <c r="I57" s="6"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -1465,7 +2145,7 @@
       <c r="H58" s="5"/>
       <c r="I58" s="6"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -1476,7 +2156,7 @@
       <c r="H59" s="5"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -1487,7 +2167,7 @@
       <c r="H60" s="5"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -1498,7 +2178,7 @@
       <c r="H61" s="5"/>
       <c r="I61" s="6"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -1509,7 +2189,7 @@
       <c r="H62" s="5"/>
       <c r="I62" s="6"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -1520,7 +2200,7 @@
       <c r="H63" s="5"/>
       <c r="I63" s="6"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -4097,5 +4777,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/SantanderCS/results/ResultListByTestModel_lsj.xlsx
+++ b/SantanderCS/results/ResultListByTestModel_lsj.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\big20\git\big20-ML-project2-team3\SantanderCS\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3029E3F8-A265-481D-AD66-08172E1712A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5BFC7B-D1D6-422B-A842-A3E659372F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C44A7696-4C41-4B13-A873-C291A9185DA3}"/>
   </bookViews>
@@ -39,7 +39,64 @@
     <author>TJ</author>
   </authors>
   <commentList>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{B062AA88-C748-44AB-933C-4E24020FE7D7}">
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{2FAA2EE8-73F8-4EF2-A2FB-AD583E875E79}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>rf_clf = RandomForestClassifier(
+    random_state      = 23,
+    n_estimators      = 390,
+    max_depth         = 25,
+    class_weight      = {0:1, 1:2},
+    min_samples_leaf  = 1,
+    min_samples_split = 7,
+    n_jobs            = -1
+)
+xgb_clf = XGBClassifier(
+    random_state      = 23,    
+    n_estimators      = 320,
+    colsample_bytree  = 0.88,
+    gamma             = 0.058, 
+    learning_rate     = 0.13,
+    max_depth         = 6,
+    scale_pos_weight  = 10,
+    min_child_weight  = 2, 
+    subsample         = 0.85,    
+    eval_metric       ='auc',
+    use_label_encoder = False,
+    n_jobs            = -1,
+)
+lgbm_clf = LGBMClassifier(
+    random_state     = 23,
+    n_estimators     = 300,
+    colsample_bytree = 0.73,
+    # max_depth      = -1,
+    learning_rate    = 0.03,
+    num_leaves       = 42,
+    reg_alpha        = 0.61,
+    reg_lambda       = 0.13,
+    subsample        = 0.97,
+    class_weight     = {0:1, 1:10},
+    n_jobs           = -1,
+)
+meta_model = LogisticRegression(
+    random_state = 23,
+    max_iter     = 1000,
+    C            = 0.029,
+    penalty      = 'l2',
+    solver       = 'lbfgs',
+    class_weight ="balanced"
+    # **lr_best_param
+)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{B062AA88-C748-44AB-933C-4E24020FE7D7}">
       <text>
         <r>
           <rPr>
@@ -136,63 +193,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="F15" authorId="0" shapeId="0" xr:uid="{2FAA2EE8-73F8-4EF2-A2FB-AD583E875E79}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>rf_clf = RandomForestClassifier(
-    random_state      = 23,
-    n_estimators      = 390,
-    max_depth         = 25,
-    class_weight      = {0:1, 1:2},
-    min_samples_leaf  = 1,
-    min_samples_split = 7,
-    n_jobs            = -1
-)
-xgb_clf = XGBClassifier(
-    random_state      = 23,    
-    n_estimators      = 320,
-    colsample_bytree  = 0.88,
-    gamma             = 0.058, 
-    learning_rate     = 0.13,
-    max_depth         = 6,
-    scale_pos_weight  = 10,
-    min_child_weight  = 2, 
-    subsample         = 0.85,    
-    eval_metric       ='auc',
-    use_label_encoder = False,
-    n_jobs            = -1,
-)
-lgbm_clf = LGBMClassifier(
-    random_state     = 23,
-    n_estimators     = 300,
-    colsample_bytree = 0.73,
-    # max_depth      = -1,
-    learning_rate    = 0.03,
-    num_leaves       = 42,
-    reg_alpha        = 0.61,
-    reg_lambda       = 0.13,
-    subsample        = 0.97,
-    class_weight     = {0:1, 1:10},
-    n_jobs           = -1,
-)
-meta_model = LogisticRegression(
-    random_state = 23,
-    max_iter     = 1000,
-    C            = 0.029,
-    penalty      = 'l2',
-    solver       = 'lbfgs',
-    class_weight ="balanced"
-    # **lr_best_param
-)</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -589,7 +589,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -728,7 +728,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -777,9 +777,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -801,9 +798,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -822,13 +816,40 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1157,80 +1178,81 @@
     <col min="7" max="7" width="9.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="8.75" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="69.75" style="29" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="69.75" style="27" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="23" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="115.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
-        <v>6</v>
+      <c r="B2" s="21" t="s">
+        <v>45</v>
       </c>
       <c r="C2" s="5">
         <v>0.2</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="16">
-        <v>0.84570000000000001</v>
-      </c>
-      <c r="H2" s="16">
-        <v>1.5299999999999999E-2</v>
-      </c>
-      <c r="I2" s="16">
-        <v>8.3000000000000001E-3</v>
-      </c>
-      <c r="J2" s="26" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="29">
+        <v>0.93</v>
+      </c>
+      <c r="H2" s="29">
+        <v>0.29330000000000001</v>
+      </c>
+      <c r="I2" s="29">
+        <v>0.88529999999999998</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
+        <f>A2+1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>6</v>
+      <c r="B3" s="21" t="s">
+        <v>45</v>
       </c>
       <c r="C3" s="5">
         <v>0.2</v>
@@ -1238,407 +1260,395 @@
       <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>17</v>
+      <c r="E3" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>47</v>
       </c>
       <c r="G3" s="5">
-        <v>0.83374000000000004</v>
+        <v>0.91149999999999998</v>
       </c>
       <c r="H3" s="5">
-        <v>4.8411000000000003E-2</v>
-      </c>
-      <c r="I3" s="5">
-        <v>2.6578000000000001E-2</v>
-      </c>
-      <c r="J3" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="20"/>
-    </row>
-    <row r="4" spans="1:12" ht="198" x14ac:dyDescent="0.3">
+        <v>0.2797</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.85570000000000002</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="19"/>
+    </row>
+    <row r="4" spans="1:12" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
-        <f t="shared" ref="A4:A14" si="0">A3+1</f>
         <v>3</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="5">
         <v>0.2</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="32">
+        <v>0.84570000000000001</v>
+      </c>
+      <c r="H4" s="32">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="I4" s="32">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="J4" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="198" x14ac:dyDescent="0.3">
+      <c r="A5" s="33">
+        <v>3</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="35">
+        <v>0.2</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E5" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0.83463600000000004</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0.28441</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0.362126</v>
-      </c>
-      <c r="J4" s="27" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B5" s="22" t="s">
+      <c r="F5" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="38">
+        <v>0.84520600000000001</v>
+      </c>
+      <c r="H5" s="38">
+        <v>0.287053</v>
+      </c>
+      <c r="I5" s="39">
+        <v>0.55980099999999999</v>
+      </c>
+      <c r="J5" s="40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="115.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0.82199999999999995</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0.51739999999999997</v>
-      </c>
-      <c r="I5" s="4">
-        <v>0.64119999999999999</v>
-      </c>
-      <c r="J5" s="27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0.2</v>
+      <c r="C6" s="30">
+        <v>0.3</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>13</v>
       </c>
       <c r="G6" s="5">
-        <v>0.81789999999999996</v>
+        <v>0.83740000000000003</v>
       </c>
       <c r="H6" s="5">
-        <v>0.40849999999999997</v>
+        <v>1.6400000000000001E-2</v>
       </c>
       <c r="I6" s="4">
-        <v>0.54149999999999998</v>
-      </c>
-      <c r="J6" s="27" t="s">
-        <v>29</v>
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="5">
         <v>0.2</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>23</v>
+        <v>39</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>36</v>
       </c>
       <c r="G7" s="5">
-        <v>0.81730000000000003</v>
+        <v>0.83640000000000003</v>
       </c>
       <c r="H7" s="5">
-        <v>0.30709999999999998</v>
+        <v>0.29070000000000001</v>
       </c>
       <c r="I7" s="4">
-        <v>0.42520000000000002</v>
-      </c>
-      <c r="J7" s="27" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
+        <v>0.37040000000000001</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="198" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B8" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="5">
         <v>0.2</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="28" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
+      <c r="E8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.83463600000000004</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.28441</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.362126</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="5">
         <v>0.2</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>31</v>
+      <c r="E9" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="28" t="s">
-        <v>34</v>
+        <v>17</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.83374000000000004</v>
+      </c>
+      <c r="H9" s="5">
+        <v>4.8411000000000003E-2</v>
+      </c>
+      <c r="I9" s="5">
+        <v>2.6578000000000001E-2</v>
+      </c>
+      <c r="J9" s="24" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B10" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="5">
         <v>0.2</v>
       </c>
-      <c r="D10" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="28" t="s">
-        <v>35</v>
+      <c r="D10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.51739999999999997</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.64119999999999999</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B11" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="5">
         <v>0.2</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>36</v>
+        <v>26</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>23</v>
       </c>
       <c r="G11" s="5">
-        <v>0.83640000000000003</v>
+        <v>0.81789999999999996</v>
       </c>
       <c r="H11" s="5">
-        <v>0.29070000000000001</v>
+        <v>0.40849999999999997</v>
       </c>
       <c r="I11" s="4">
-        <v>0.37040000000000001</v>
-      </c>
-      <c r="J11" s="27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="115.5" x14ac:dyDescent="0.3">
+        <v>0.54149999999999998</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="24">
-        <v>0.3</v>
+      <c r="C12" s="15">
+        <v>0.2</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="33">
-        <v>0.83740000000000003</v>
+        <v>27</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.81730000000000003</v>
       </c>
       <c r="H12" s="1">
-        <v>1.6400000000000001E-2</v>
+        <v>0.30709999999999998</v>
       </c>
       <c r="I12" s="2">
-        <v>8.8999999999999999E-3</v>
-      </c>
-      <c r="J12" s="29" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="198" x14ac:dyDescent="0.3">
+        <v>0.42520000000000002</v>
+      </c>
+      <c r="J12" s="27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B13" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="5">
         <v>0.2</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0.84520600000000001</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0.287053</v>
-      </c>
-      <c r="I13" s="4">
-        <v>0.55980099999999999</v>
-      </c>
-      <c r="J13" s="27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="E13" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="26" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>45</v>
+        <v>3</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>6</v>
       </c>
       <c r="C14" s="5">
         <v>0.2</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0.91149999999999998</v>
-      </c>
-      <c r="H14" s="5">
-        <v>0.2797</v>
-      </c>
-      <c r="I14" s="4">
-        <v>0.85570000000000002</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="148.5" x14ac:dyDescent="0.3">
+      <c r="E14" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="181.5" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
-        <f>A14+1</f>
-        <v>14</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>45</v>
+        <v>3</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>6</v>
       </c>
       <c r="C15" s="5">
         <v>0.2</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="31">
-        <v>0.93</v>
-      </c>
-      <c r="H15" s="31">
-        <v>0.29330000000000001</v>
-      </c>
-      <c r="I15" s="32">
-        <v>0.88529999999999998</v>
-      </c>
-      <c r="J15" s="30" t="s">
-        <v>50</v>
+      <c r="E15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="26" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
-      <c r="B16" s="22"/>
+      <c r="B16" s="21"/>
       <c r="C16" s="5"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -1646,11 +1656,11 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="27"/>
+      <c r="J16" s="25"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
-      <c r="B17" s="22"/>
+      <c r="B17" s="21"/>
       <c r="C17" s="5"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -1658,7 +1668,7 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="27"/>
+      <c r="J17" s="25"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
@@ -1670,7 +1680,7 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="27"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
@@ -1682,7 +1692,7 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="27"/>
+      <c r="J19" s="25"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
@@ -1694,7 +1704,7 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="27"/>
+      <c r="J20" s="25"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
@@ -1706,7 +1716,7 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="27"/>
+      <c r="J21" s="25"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
@@ -1718,7 +1728,7 @@
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="27"/>
+      <c r="J22" s="25"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
@@ -1730,7 +1740,7 @@
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="27"/>
+      <c r="J23" s="25"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
@@ -1742,7 +1752,7 @@
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="27"/>
+      <c r="J24" s="25"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
@@ -1754,7 +1764,7 @@
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="27"/>
+      <c r="J25" s="25"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
@@ -1766,7 +1776,7 @@
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="27"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
@@ -1778,7 +1788,7 @@
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="27"/>
+      <c r="J27" s="25"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
@@ -1790,7 +1800,7 @@
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="27"/>
+      <c r="J28" s="25"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
@@ -1802,7 +1812,7 @@
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="27"/>
+      <c r="J29" s="25"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
@@ -1814,7 +1824,7 @@
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="27"/>
+      <c r="J30" s="25"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
@@ -1826,7 +1836,7 @@
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="27"/>
+      <c r="J31" s="25"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
@@ -1838,7 +1848,7 @@
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="4"/>
-      <c r="J32" s="27"/>
+      <c r="J32" s="25"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
@@ -1850,7 +1860,7 @@
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="4"/>
-      <c r="J33" s="27"/>
+      <c r="J33" s="25"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="4"/>
@@ -1862,7 +1872,7 @@
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="27"/>
+      <c r="J34" s="25"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="4"/>
@@ -1874,7 +1884,7 @@
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="27"/>
+      <c r="J35" s="25"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
@@ -1886,7 +1896,7 @@
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="27"/>
+      <c r="J36" s="25"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
@@ -1898,7 +1908,7 @@
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="27"/>
+      <c r="J37" s="25"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
@@ -1910,7 +1920,7 @@
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="4"/>
-      <c r="J38" s="27"/>
+      <c r="J38" s="25"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
@@ -1922,7 +1932,7 @@
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="27"/>
+      <c r="J39" s="25"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
@@ -1934,7 +1944,7 @@
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="27"/>
+      <c r="J40" s="25"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
@@ -1946,7 +1956,7 @@
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="4"/>
-      <c r="J41" s="27"/>
+      <c r="J41" s="25"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
@@ -1958,7 +1968,7 @@
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="27"/>
+      <c r="J42" s="25"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
@@ -1970,7 +1980,7 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="27"/>
+      <c r="J43" s="25"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
@@ -1982,7 +1992,7 @@
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="4"/>
-      <c r="J44" s="27"/>
+      <c r="J44" s="25"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
@@ -1994,7 +2004,7 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="4"/>
-      <c r="J45" s="27"/>
+      <c r="J45" s="25"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
@@ -2006,7 +2016,7 @@
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="4"/>
-      <c r="J46" s="27"/>
+      <c r="J46" s="25"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
@@ -2018,7 +2028,7 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="4"/>
-      <c r="J47" s="27"/>
+      <c r="J47" s="25"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
@@ -2030,7 +2040,7 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="27"/>
+      <c r="J48" s="25"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
@@ -2042,7 +2052,7 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="4"/>
-      <c r="J49" s="27"/>
+      <c r="J49" s="25"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
@@ -2054,7 +2064,7 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="4"/>
-      <c r="J50" s="27"/>
+      <c r="J50" s="25"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
@@ -2066,7 +2076,7 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="4"/>
-      <c r="J51" s="27"/>
+      <c r="J51" s="25"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="11"/>
@@ -2077,7 +2087,7 @@
       <c r="F52" s="15"/>
       <c r="G52" s="15"/>
       <c r="H52" s="15"/>
-      <c r="I52" s="19"/>
+      <c r="I52" s="18"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
@@ -4775,8 +4785,14 @@
       <c r="I297" s="10"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J297">
+    <sortCondition descending="1" ref="G2:G297"/>
+    <sortCondition descending="1" ref="H2:H297"/>
+    <sortCondition descending="1" ref="I2:I297"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>